--- a/src/data/calibration_data_line.xlsx
+++ b/src/data/calibration_data_line.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matthew Tan\Documents\ECSE211\ECSE211_W26_Final_Project\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{ACED32CB-53AA-4677-8CF2-6612F2CDCD93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92EF003C-6D0C-4447-A245-6E5C6D941833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CDA1F517-FBE1-4F84-B1BC-BE521F0666B7}"/>
   </bookViews>
   <sheets>
     <sheet name="calibration_data_line" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>R</t>
   </si>
@@ -31,10 +44,16 @@
     <t>B</t>
   </si>
   <si>
-    <t>avg</t>
+    <t>vector avg</t>
   </si>
   <si>
-    <t>std dev</t>
+    <t>vector std dev</t>
+  </si>
+  <si>
+    <t>ratio avg</t>
+  </si>
+  <si>
+    <t>ratio std dev</t>
   </si>
 </sst>
 </file>
@@ -895,10 +914,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{633C60D2-9F75-4AD9-A1A9-3937482F1E30}">
-  <dimension ref="A1:L90"/>
+  <dimension ref="A1:Q90"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -909,7 +928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>34</v>
       </c>
@@ -931,23 +950,35 @@
         <f t="shared" si="0"/>
         <v>0.73579006829971627</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2">
+        <f>A2/($A2+$B2+$C2)</f>
+        <v>0.34</v>
+      </c>
+      <c r="J2">
+        <f t="shared" ref="J2:K2" si="1">B2/($A2+$B2+$C2)</f>
+        <v>0.22</v>
+      </c>
+      <c r="K2">
+        <f t="shared" si="1"/>
+        <v>0.44</v>
+      </c>
+      <c r="N2" t="s">
         <v>3</v>
       </c>
-      <c r="J2">
+      <c r="O2">
         <f>AVERAGE(E2:E90)</f>
         <v>0.5278860104459917</v>
       </c>
-      <c r="K2">
-        <f t="shared" ref="K2:L2" si="1">AVERAGE(F2:F90)</f>
+      <c r="P2">
+        <f>AVERAGE(F2:F90)</f>
         <v>0.43604605442402439</v>
       </c>
-      <c r="L2">
-        <f t="shared" si="1"/>
+      <c r="Q2">
+        <f>AVERAGE(G2:G90)</f>
         <v>0.71772539289779858</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>34</v>
       </c>
@@ -969,23 +1000,35 @@
         <f t="shared" ref="G3:G65" si="4">C3/($A3^2 + $B3^2 + $C3^2)^0.5</f>
         <v>0.72332784352142565</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3">
+        <f t="shared" ref="I3:I66" si="5">A3/($A3+$B3+$C3)</f>
+        <v>0.34</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J66" si="6">B3/($A3+$B3+$C3)</f>
+        <v>0.23</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K66" si="7">C3/($A3+$B3+$C3)</f>
+        <v>0.43</v>
+      </c>
+      <c r="N3" t="s">
         <v>4</v>
       </c>
-      <c r="J3">
+      <c r="O3">
         <f>_xlfn.STDEV.P(E2:E90)</f>
         <v>3.1268985702295617E-2</v>
       </c>
-      <c r="K3">
-        <f t="shared" ref="K3:L3" si="5">_xlfn.STDEV.P(F2:F90)</f>
+      <c r="P3">
+        <f>_xlfn.STDEV.P(F2:F90)</f>
         <v>0.10196329668641484</v>
       </c>
-      <c r="L3">
-        <f t="shared" si="5"/>
+      <c r="Q3">
+        <f>_xlfn.STDEV.P(G2:G90)</f>
         <v>6.8528792841722738E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>32</v>
       </c>
@@ -1007,8 +1050,20 @@
         <f t="shared" si="4"/>
         <v>0.75907211527658969</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I4">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="6"/>
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="7"/>
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>32</v>
       </c>
@@ -1030,8 +1085,35 @@
         <f t="shared" si="4"/>
         <v>0.75907211527658969</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I5">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="6"/>
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="7"/>
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="N5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O5">
+        <f>AVERAGE(I2:I90)</f>
+        <v>0.31399623673366556</v>
+      </c>
+      <c r="P5">
+        <f t="shared" ref="P5:Q5" si="8">AVERAGE(J2:J90)</f>
+        <v>0.25826765168042942</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="8"/>
+        <v>0.42773611158590485</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>32</v>
       </c>
@@ -1053,8 +1135,35 @@
         <f t="shared" si="4"/>
         <v>0.76172779019872416</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I6">
+        <f t="shared" si="5"/>
+        <v>0.32653061224489793</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="6"/>
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="7"/>
+        <v>0.45918367346938777</v>
+      </c>
+      <c r="N6" t="s">
+        <v>6</v>
+      </c>
+      <c r="O6">
+        <f>_xlfn.STDEV.P(I2:I90)</f>
+        <v>1.9151279347868234E-2</v>
+      </c>
+      <c r="P6">
+        <f t="shared" ref="P6:Q6" si="9">_xlfn.STDEV.P(J2:J90)</f>
+        <v>5.5094537494180307E-2</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="9"/>
+        <v>4.8542011784032404E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>34</v>
       </c>
@@ -1076,8 +1185,20 @@
         <f t="shared" si="4"/>
         <v>0.73579006829971627</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I7">
+        <f t="shared" si="5"/>
+        <v>0.34</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="6"/>
+        <v>0.22</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="7"/>
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>33</v>
       </c>
@@ -1099,8 +1220,20 @@
         <f t="shared" si="4"/>
         <v>0.75020842017909617</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I8">
+        <f t="shared" si="5"/>
+        <v>0.33</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="6"/>
+        <v>0.22</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="7"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>34</v>
       </c>
@@ -1122,8 +1255,20 @@
         <f t="shared" si="4"/>
         <v>0.73690227526401386</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I9">
+        <f t="shared" si="5"/>
+        <v>0.35051546391752575</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="6"/>
+        <v>0.20618556701030927</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="7"/>
+        <v>0.44329896907216493</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>34</v>
       </c>
@@ -1145,8 +1290,20 @@
         <f t="shared" si="4"/>
         <v>0.74331949691125676</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I10">
+        <f t="shared" si="5"/>
+        <v>0.33663366336633666</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="6"/>
+        <v>0.21782178217821782</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="7"/>
+        <v>0.44554455445544555</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>33</v>
       </c>
@@ -1168,8 +1325,20 @@
         <f t="shared" si="4"/>
         <v>0.72820595415852263</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I11">
+        <f t="shared" si="5"/>
+        <v>0.35106382978723405</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="6"/>
+        <v>0.21276595744680851</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="7"/>
+        <v>0.43617021276595747</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>35</v>
       </c>
@@ -1191,8 +1360,20 @@
         <f t="shared" si="4"/>
         <v>0.7287925259999315</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I12">
+        <f t="shared" si="5"/>
+        <v>0.34653465346534651</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="6"/>
+        <v>0.21782178217821782</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="7"/>
+        <v>0.43564356435643564</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>35</v>
       </c>
@@ -1214,8 +1395,20 @@
         <f t="shared" si="4"/>
         <v>0.7287925259999315</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I13">
+        <f t="shared" si="5"/>
+        <v>0.34653465346534651</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="6"/>
+        <v>0.21782178217821782</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="7"/>
+        <v>0.43564356435643564</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>34</v>
       </c>
@@ -1237,8 +1430,20 @@
         <f t="shared" si="4"/>
         <v>0.74612036992657116</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I14">
+        <f t="shared" si="5"/>
+        <v>0.3300970873786408</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="6"/>
+        <v>0.22330097087378642</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="7"/>
+        <v>0.44660194174757284</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>33</v>
       </c>
@@ -1260,8 +1465,20 @@
         <f t="shared" si="4"/>
         <v>0.74084329419844608</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I15">
+        <f t="shared" si="5"/>
+        <v>0.35106382978723405</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="6"/>
+        <v>0.20212765957446807</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="7"/>
+        <v>0.44680851063829785</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>35</v>
       </c>
@@ -1283,8 +1500,20 @@
         <f t="shared" si="4"/>
         <v>0.72528014894408011</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I16">
+        <f t="shared" si="5"/>
+        <v>0.35353535353535354</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="6"/>
+        <v>0.21212121212121213</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="7"/>
+        <v>0.43434343434343436</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>34</v>
       </c>
@@ -1306,8 +1535,20 @@
         <f t="shared" si="4"/>
         <v>0.74154976225203517</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I17">
+        <f t="shared" si="5"/>
+        <v>0.32692307692307693</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="6"/>
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="7"/>
+        <v>0.44230769230769229</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>31</v>
       </c>
@@ -1329,8 +1570,20 @@
         <f t="shared" si="4"/>
         <v>0.74818016531685716</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I18">
+        <f t="shared" si="5"/>
+        <v>0.34065934065934067</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="6"/>
+        <v>0.2087912087912088</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="7"/>
+        <v>0.45054945054945056</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>33</v>
       </c>
@@ -1352,8 +1605,20 @@
         <f t="shared" si="4"/>
         <v>0.75020842017909617</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I19">
+        <f t="shared" si="5"/>
+        <v>0.33</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="6"/>
+        <v>0.22</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="7"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>34</v>
       </c>
@@ -1375,8 +1640,20 @@
         <f t="shared" si="4"/>
         <v>0.72446103862743383</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I20">
+        <f t="shared" si="5"/>
+        <v>0.35051546391752575</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="6"/>
+        <v>0.21649484536082475</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="7"/>
+        <v>0.4329896907216495</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>35</v>
       </c>
@@ -1398,8 +1675,20 @@
         <f t="shared" si="4"/>
         <v>0.73043483481225846</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I21">
+        <f t="shared" si="5"/>
+        <v>0.330188679245283</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="6"/>
+        <v>0.23584905660377359</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="7"/>
+        <v>0.43396226415094341</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>33</v>
       </c>
@@ -1421,8 +1710,20 @@
         <f t="shared" si="4"/>
         <v>0.73973192075921357</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I22">
+        <f t="shared" si="5"/>
+        <v>0.34020618556701032</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="6"/>
+        <v>0.21649484536082475</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="7"/>
+        <v>0.44329896907216493</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>34</v>
       </c>
@@ -1444,8 +1745,20 @@
         <f t="shared" si="4"/>
         <v>0.73120375682577954</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I23">
+        <f t="shared" si="5"/>
+        <v>0.33663366336633666</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="6"/>
+        <v>0.22772277227722773</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="7"/>
+        <v>0.43564356435643564</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>33</v>
       </c>
@@ -1467,8 +1780,20 @@
         <f t="shared" si="4"/>
         <v>0.75736198796071552</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I24">
+        <f t="shared" si="5"/>
+        <v>0.32673267326732675</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="6"/>
+        <v>0.21782178217821782</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="7"/>
+        <v>0.45544554455445546</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>32</v>
       </c>
@@ -1490,8 +1815,20 @@
         <f t="shared" si="4"/>
         <v>0.75161502454833551</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I25">
+        <f t="shared" si="5"/>
+        <v>0.33684210526315789</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="6"/>
+        <v>0.21052631578947367</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="7"/>
+        <v>0.45263157894736844</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>33</v>
       </c>
@@ -1513,8 +1850,20 @@
         <f t="shared" si="4"/>
         <v>0.73973192075921357</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I26">
+        <f t="shared" si="5"/>
+        <v>0.34020618556701032</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="6"/>
+        <v>0.21649484536082475</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="7"/>
+        <v>0.44329896907216493</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>33</v>
       </c>
@@ -1536,8 +1885,20 @@
         <f t="shared" si="4"/>
         <v>0.7547319081399414</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I27">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="6"/>
+        <v>0.21212121212121213</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="7"/>
+        <v>0.45454545454545453</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>35</v>
       </c>
@@ -1559,8 +1920,20 @@
         <f t="shared" si="4"/>
         <v>0.73202188940848445</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I28">
+        <f t="shared" si="5"/>
+        <v>0.33980582524271846</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="6"/>
+        <v>0.22330097087378642</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="7"/>
+        <v>0.43689320388349512</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>33</v>
       </c>
@@ -1582,8 +1955,20 @@
         <f t="shared" si="4"/>
         <v>0.7455605639302948</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I29">
+        <f t="shared" si="5"/>
+        <v>0.32673267326732675</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="6"/>
+        <v>0.22772277227722773</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="7"/>
+        <v>0.44554455445544555</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>27</v>
       </c>
@@ -1605,8 +1990,20 @@
         <f t="shared" si="4"/>
         <v>0.77538828587039588</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I30">
+        <f t="shared" si="5"/>
+        <v>0.3</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="6"/>
+        <v>0.23333333333333334</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="7"/>
+        <v>0.46666666666666667</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>34</v>
       </c>
@@ -1628,8 +2025,20 @@
         <f t="shared" si="4"/>
         <v>0.72797752399170124</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I31">
+        <f t="shared" si="5"/>
+        <v>0.34343434343434343</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="6"/>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="7"/>
+        <v>0.43434343434343436</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>29</v>
       </c>
@@ -1651,8 +2060,20 @@
         <f t="shared" si="4"/>
         <v>0.77563903363834019</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I32">
+        <f t="shared" si="5"/>
+        <v>0.30851063829787234</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="6"/>
+        <v>0.22340425531914893</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="7"/>
+        <v>0.46808510638297873</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26</v>
       </c>
@@ -1674,8 +2095,20 @@
         <f t="shared" si="4"/>
         <v>0.79507028125616175</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I33">
+        <f t="shared" si="5"/>
+        <v>0.29213483146067415</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="6"/>
+        <v>0.2247191011235955</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="7"/>
+        <v>0.48314606741573035</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>26</v>
       </c>
@@ -1697,8 +2130,20 @@
         <f t="shared" si="4"/>
         <v>0.79507028125616175</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I34">
+        <f t="shared" si="5"/>
+        <v>0.29213483146067415</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="6"/>
+        <v>0.2247191011235955</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="7"/>
+        <v>0.48314606741573035</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>30</v>
       </c>
@@ -1720,8 +2165,20 @@
         <f t="shared" si="4"/>
         <v>0.76862491105268882</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I35">
+        <f t="shared" si="5"/>
+        <v>0.31578947368421051</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="6"/>
+        <v>0.22105263157894736</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="7"/>
+        <v>0.4631578947368421</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>29</v>
       </c>
@@ -1743,8 +2200,20 @@
         <f t="shared" si="4"/>
         <v>0.77050822146807285</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I36">
+        <f t="shared" si="5"/>
+        <v>0.30526315789473685</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="6"/>
+        <v>0.23157894736842105</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="7"/>
+        <v>0.4631578947368421</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>27</v>
       </c>
@@ -1766,8 +2235,20 @@
         <f t="shared" si="4"/>
         <v>0.78796351502299111</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I37">
+        <f t="shared" si="5"/>
+        <v>0.3</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="6"/>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="7"/>
+        <v>0.4777777777777778</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>29</v>
       </c>
@@ -1789,8 +2270,20 @@
         <f t="shared" si="4"/>
         <v>0.77050822146807285</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I38">
+        <f t="shared" si="5"/>
+        <v>0.30526315789473685</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="6"/>
+        <v>0.23157894736842105</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="7"/>
+        <v>0.4631578947368421</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>28</v>
       </c>
@@ -1812,8 +2305,20 @@
         <f t="shared" si="4"/>
         <v>0.77733177867133063</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I39">
+        <f t="shared" si="5"/>
+        <v>0.2978723404255319</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="6"/>
+        <v>0.23404255319148937</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="7"/>
+        <v>0.46808510638297873</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>28</v>
       </c>
@@ -1835,8 +2340,20 @@
         <f t="shared" si="4"/>
         <v>0.79437881797704524</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I40">
+        <f t="shared" si="5"/>
+        <v>0.30107526881720431</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="6"/>
+        <v>0.21505376344086022</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="7"/>
+        <v>0.4838709677419355</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>28</v>
       </c>
@@ -1858,8 +2375,20 @@
         <f t="shared" si="4"/>
         <v>0.78078641867407539</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I41">
+        <f t="shared" si="5"/>
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="6"/>
+        <v>0.21978021978021978</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="7"/>
+        <v>0.47252747252747251</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>29</v>
       </c>
@@ -1881,8 +2410,20 @@
         <f t="shared" si="4"/>
         <v>0.77748158302322412</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I42">
+        <f t="shared" si="5"/>
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="6"/>
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="7"/>
+        <v>0.46875</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>29</v>
       </c>
@@ -1904,8 +2445,20 @@
         <f t="shared" si="4"/>
         <v>0.77563903363834019</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I43">
+        <f t="shared" si="5"/>
+        <v>0.30851063829787234</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="6"/>
+        <v>0.22340425531914893</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="7"/>
+        <v>0.46808510638297873</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>28</v>
       </c>
@@ -1927,8 +2480,20 @@
         <f t="shared" si="4"/>
         <v>0.78935221737632633</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I44">
+        <f t="shared" si="5"/>
+        <v>0.2978723404255319</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="6"/>
+        <v>0.22340425531914893</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="7"/>
+        <v>0.47872340425531917</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>28</v>
       </c>
@@ -1950,8 +2515,20 @@
         <f t="shared" si="4"/>
         <v>0.77556200371119299</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I45">
+        <f t="shared" si="5"/>
+        <v>0.30434782608695654</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="6"/>
+        <v>0.22826086956521738</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="7"/>
+        <v>0.46739130434782611</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>28</v>
       </c>
@@ -1973,8 +2550,20 @@
         <f t="shared" si="4"/>
         <v>0.77733177867133063</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I46">
+        <f t="shared" si="5"/>
+        <v>0.2978723404255319</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="6"/>
+        <v>0.23404255319148937</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="7"/>
+        <v>0.46808510638297873</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>27</v>
       </c>
@@ -1996,8 +2585,20 @@
         <f t="shared" si="4"/>
         <v>0.78796351502299111</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I47">
+        <f t="shared" si="5"/>
+        <v>0.3</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="6"/>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="7"/>
+        <v>0.4777777777777778</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>27</v>
       </c>
@@ -2019,8 +2620,20 @@
         <f t="shared" si="4"/>
         <v>0.79317435215036591</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I48">
+        <f t="shared" si="5"/>
+        <v>0.30337078651685395</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="6"/>
+        <v>0.21348314606741572</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="7"/>
+        <v>0.48314606741573035</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>26</v>
       </c>
@@ -2042,8 +2655,20 @@
         <f t="shared" si="4"/>
         <v>0.80696597205447129</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I49">
+        <f t="shared" si="5"/>
+        <v>0.29213483146067415</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="6"/>
+        <v>0.21348314606741572</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="7"/>
+        <v>0.4943820224719101</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>29</v>
       </c>
@@ -2065,8 +2690,20 @@
         <f t="shared" si="4"/>
         <v>0.77355147018324111</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I50">
+        <f t="shared" si="5"/>
+        <v>0.31521739130434784</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="6"/>
+        <v>0.21739130434782608</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="7"/>
+        <v>0.46739130434782611</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>26</v>
       </c>
@@ -2088,8 +2725,20 @@
         <f t="shared" si="4"/>
         <v>0.80042435037868553</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I51">
+        <f t="shared" si="5"/>
+        <v>0.29545454545454547</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="6"/>
+        <v>0.21590909090909091</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="7"/>
+        <v>0.48863636363636365</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>27</v>
       </c>
@@ -2111,8 +2760,20 @@
         <f t="shared" si="4"/>
         <v>0.78796351502299111</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I52">
+        <f t="shared" si="5"/>
+        <v>0.3</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="6"/>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="7"/>
+        <v>0.4777777777777778</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>29</v>
       </c>
@@ -2134,8 +2795,20 @@
         <f t="shared" si="4"/>
         <v>0.77390207832303959</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I53">
+        <f t="shared" si="5"/>
+        <v>0.29292929292929293</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="6"/>
+        <v>0.24242424242424243</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="7"/>
+        <v>0.46464646464646464</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>28</v>
       </c>
@@ -2157,8 +2830,20 @@
         <f t="shared" si="4"/>
         <v>0.77354494211794511</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I54">
+        <f t="shared" si="5"/>
+        <v>0.31111111111111112</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="6"/>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="7"/>
+        <v>0.46666666666666667</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>27</v>
       </c>
@@ -2180,8 +2865,20 @@
         <f t="shared" si="4"/>
         <v>0.78259469402596171</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I55">
+        <f t="shared" si="5"/>
+        <v>0.2967032967032967</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="6"/>
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="7"/>
+        <v>0.47252747252747251</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>28</v>
       </c>
@@ -2203,8 +2900,20 @@
         <f t="shared" si="4"/>
         <v>0.78078641867407539</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I56">
+        <f t="shared" si="5"/>
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="6"/>
+        <v>0.21978021978021978</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="7"/>
+        <v>0.47252747252747251</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>29</v>
       </c>
@@ -2226,8 +2935,20 @@
         <f t="shared" si="4"/>
         <v>0.76099944650683971</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I57">
+        <f t="shared" si="5"/>
+        <v>0.31521739130434784</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="6"/>
+        <v>0.22826086956521738</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="7"/>
+        <v>0.45652173913043476</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>28</v>
       </c>
@@ -2249,8 +2970,20 @@
         <f t="shared" si="4"/>
         <v>0.80000865346652483</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I58">
+        <f t="shared" si="5"/>
+        <v>0.32183908045977011</v>
+      </c>
+      <c r="J58">
+        <f t="shared" si="6"/>
+        <v>0.18390804597701149</v>
+      </c>
+      <c r="K58">
+        <f t="shared" si="7"/>
+        <v>0.4942528735632184</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>27</v>
       </c>
@@ -2272,8 +3005,20 @@
         <f t="shared" si="4"/>
         <v>0.80127514102023301</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I59">
+        <f t="shared" si="5"/>
+        <v>0.29347826086956524</v>
+      </c>
+      <c r="J59">
+        <f t="shared" si="6"/>
+        <v>0.21739130434782608</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="7"/>
+        <v>0.4891304347826087</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>27</v>
       </c>
@@ -2295,8 +3040,20 @@
         <f t="shared" si="4"/>
         <v>0.77344724485215866</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I60">
+        <f t="shared" si="5"/>
+        <v>0.30681818181818182</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="6"/>
+        <v>0.22727272727272727</v>
+      </c>
+      <c r="K60">
+        <f t="shared" si="7"/>
+        <v>0.46590909090909088</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>26</v>
       </c>
@@ -2318,8 +3075,20 @@
         <f t="shared" si="4"/>
         <v>0.80042435037868553</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I61">
+        <f t="shared" si="5"/>
+        <v>0.29545454545454547</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="6"/>
+        <v>0.21590909090909091</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="7"/>
+        <v>0.48863636363636365</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>16</v>
       </c>
@@ -2341,8 +3110,20 @@
         <f t="shared" si="4"/>
         <v>0.6312327194758407</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I62">
+        <f t="shared" si="5"/>
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="6"/>
+        <v>0.32692307692307693</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="7"/>
+        <v>0.36538461538461536</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>15</v>
       </c>
@@ -2364,8 +3145,20 @@
         <f t="shared" si="4"/>
         <v>0.63441663916521718</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I63">
+        <f t="shared" si="5"/>
+        <v>0.30612244897959184</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="6"/>
+        <v>0.32653061224489793</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="7"/>
+        <v>0.36734693877551022</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>15</v>
       </c>
@@ -2387,8 +3180,20 @@
         <f t="shared" si="4"/>
         <v>0.64231723359367265</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I64">
+        <f t="shared" si="5"/>
+        <v>0.29411764705882354</v>
+      </c>
+      <c r="J64">
+        <f t="shared" si="6"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="7"/>
+        <v>0.37254901960784315</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>16</v>
       </c>
@@ -2410,8 +3215,20 @@
         <f t="shared" si="4"/>
         <v>0.61060817839748249</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I65">
+        <f t="shared" si="5"/>
+        <v>0.31372549019607843</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="6"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="7"/>
+        <v>0.35294117647058826</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>15</v>
       </c>
@@ -2422,19 +3239,31 @@
         <v>18</v>
       </c>
       <c r="E66">
-        <f t="shared" ref="E66:E90" si="6">A66/($A66^2 + $B66^2 + $C66^2)^0.5</f>
+        <f t="shared" ref="E66:E90" si="10">A66/($A66^2 + $B66^2 + $C66^2)^0.5</f>
         <v>0.5181664018901001</v>
       </c>
       <c r="F66">
-        <f t="shared" ref="F66:F90" si="7">B66/($A66^2 + $B66^2 + $C66^2)^0.5</f>
+        <f t="shared" ref="F66:F90" si="11">B66/($A66^2 + $B66^2 + $C66^2)^0.5</f>
         <v>0.58725525547544677</v>
       </c>
       <c r="G66">
-        <f t="shared" ref="G66:G90" si="8">C66/($A66^2 + $B66^2 + $C66^2)^0.5</f>
+        <f t="shared" ref="G66:G90" si="12">C66/($A66^2 + $B66^2 + $C66^2)^0.5</f>
         <v>0.6217996822681201</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I66">
+        <f t="shared" si="5"/>
+        <v>0.3</v>
+      </c>
+      <c r="J66">
+        <f t="shared" si="6"/>
+        <v>0.34</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="7"/>
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>15</v>
       </c>
@@ -2445,19 +3274,31 @@
         <v>18</v>
       </c>
       <c r="E67">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.528680532637681</v>
       </c>
       <c r="F67">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.56392590148019306</v>
       </c>
       <c r="G67">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.63441663916521718</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I67">
+        <f t="shared" ref="I67:I90" si="13">A67/($A67+$B67+$C67)</f>
+        <v>0.30612244897959184</v>
+      </c>
+      <c r="J67">
+        <f t="shared" ref="J67:J90" si="14">B67/($A67+$B67+$C67)</f>
+        <v>0.32653061224489793</v>
+      </c>
+      <c r="K67">
+        <f t="shared" ref="K67:K90" si="15">C67/($A67+$B67+$C67)</f>
+        <v>0.36734693877551022</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>16</v>
       </c>
@@ -2468,19 +3309,31 @@
         <v>19</v>
       </c>
       <c r="E68">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.53156439534807631</v>
       </c>
       <c r="F68">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.56478717005733114</v>
       </c>
       <c r="G68">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.6312327194758407</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I68">
+        <f t="shared" si="13"/>
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="J68">
+        <f t="shared" si="14"/>
+        <v>0.32692307692307693</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="15"/>
+        <v>0.36538461538461536</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>18</v>
       </c>
@@ -2491,19 +3344,31 @@
         <v>20</v>
       </c>
       <c r="E69">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.53689498764470422</v>
       </c>
       <c r="F69">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.5965499862718936</v>
       </c>
       <c r="G69">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.5965499862718936</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I69">
+        <f t="shared" si="13"/>
+        <v>0.31034482758620691</v>
+      </c>
+      <c r="J69">
+        <f t="shared" si="14"/>
+        <v>0.34482758620689657</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="15"/>
+        <v>0.34482758620689657</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>16</v>
       </c>
@@ -2514,19 +3379,31 @@
         <v>18</v>
       </c>
       <c r="E70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.53215208419019144</v>
       </c>
       <c r="F70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.5986710947139654</v>
       </c>
       <c r="G70">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.5986710947139654</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I70">
+        <f t="shared" si="13"/>
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="J70">
+        <f t="shared" si="14"/>
+        <v>0.34615384615384615</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="15"/>
+        <v>0.34615384615384615</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>16</v>
       </c>
@@ -2537,19 +3414,31 @@
         <v>18</v>
       </c>
       <c r="E71">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.54276282524220665</v>
       </c>
       <c r="F71">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.57668550181984457</v>
       </c>
       <c r="G71">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.61060817839748249</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I71">
+        <f t="shared" si="13"/>
+        <v>0.31372549019607843</v>
+      </c>
+      <c r="J71">
+        <f t="shared" si="14"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="15"/>
+        <v>0.35294117647058826</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>16</v>
       </c>
@@ -2560,19 +3449,31 @@
         <v>21</v>
       </c>
       <c r="E72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.50954380423878565</v>
       </c>
       <c r="F72">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.54139029200370969</v>
       </c>
       <c r="G72">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.66877624306340611</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I72">
+        <f t="shared" si="13"/>
+        <v>0.29629629629629628</v>
+      </c>
+      <c r="J72">
+        <f t="shared" si="14"/>
+        <v>0.31481481481481483</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="15"/>
+        <v>0.3888888888888889</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>15</v>
       </c>
@@ -2583,19 +3484,31 @@
         <v>19</v>
       </c>
       <c r="E73">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.50709255283710997</v>
       </c>
       <c r="F73">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.57470489321539131</v>
       </c>
       <c r="G73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.64231723359367265</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I73">
+        <f t="shared" si="13"/>
+        <v>0.29411764705882354</v>
+      </c>
+      <c r="J73">
+        <f t="shared" si="14"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K73">
+        <f t="shared" si="15"/>
+        <v>0.37254901960784315</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>16</v>
       </c>
@@ -2606,19 +3519,31 @@
         <v>18</v>
       </c>
       <c r="E74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.54276282524220665</v>
       </c>
       <c r="F74">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.57668550181984457</v>
       </c>
       <c r="G74">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.61060817839748249</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I74">
+        <f t="shared" si="13"/>
+        <v>0.31372549019607843</v>
+      </c>
+      <c r="J74">
+        <f t="shared" si="14"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K74">
+        <f t="shared" si="15"/>
+        <v>0.35294117647058826</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>16</v>
       </c>
@@ -2629,19 +3554,31 @@
         <v>18</v>
       </c>
       <c r="E75">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.54276282524220665</v>
       </c>
       <c r="F75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.57668550181984457</v>
       </c>
       <c r="G75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.61060817839748249</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I75">
+        <f t="shared" si="13"/>
+        <v>0.31372549019607843</v>
+      </c>
+      <c r="J75">
+        <f t="shared" si="14"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K75">
+        <f t="shared" si="15"/>
+        <v>0.35294117647058826</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>17</v>
       </c>
@@ -2652,19 +3589,31 @@
         <v>20</v>
       </c>
       <c r="E76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.51515151515151514</v>
       </c>
       <c r="F76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.60606060606060608</v>
       </c>
       <c r="G76">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.60606060606060608</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I76">
+        <f t="shared" si="13"/>
+        <v>0.2982456140350877</v>
+      </c>
+      <c r="J76">
+        <f t="shared" si="14"/>
+        <v>0.35087719298245612</v>
+      </c>
+      <c r="K76">
+        <f t="shared" si="15"/>
+        <v>0.35087719298245612</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>14</v>
       </c>
@@ -2675,19 +3624,31 @@
         <v>19</v>
       </c>
       <c r="E77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.48132991492077026</v>
       </c>
       <c r="F77">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.58447203954664961</v>
       </c>
       <c r="G77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.65323345596390248</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I77">
+        <f t="shared" si="13"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J77">
+        <f t="shared" si="14"/>
+        <v>0.34</v>
+      </c>
+      <c r="K77">
+        <f t="shared" si="15"/>
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>17</v>
       </c>
@@ -2698,19 +3659,31 @@
         <v>21</v>
       </c>
       <c r="E78">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.50571949971242014</v>
       </c>
       <c r="F78">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.59496411730872967</v>
       </c>
       <c r="G78">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.62471232317416614</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I78">
+        <f t="shared" si="13"/>
+        <v>0.29310344827586204</v>
+      </c>
+      <c r="J78">
+        <f t="shared" si="14"/>
+        <v>0.34482758620689657</v>
+      </c>
+      <c r="K78">
+        <f t="shared" si="15"/>
+        <v>0.36206896551724138</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>15</v>
       </c>
@@ -2721,19 +3694,31 @@
         <v>20</v>
       </c>
       <c r="E79">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.49615590124171688</v>
       </c>
       <c r="F79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.56231002140727915</v>
       </c>
       <c r="G79">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.66154120165562247</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I79">
+        <f t="shared" si="13"/>
+        <v>0.28846153846153844</v>
+      </c>
+      <c r="J79">
+        <f t="shared" si="14"/>
+        <v>0.32692307692307693</v>
+      </c>
+      <c r="K79">
+        <f t="shared" si="15"/>
+        <v>0.38461538461538464</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>15</v>
       </c>
@@ -2744,19 +3729,31 @@
         <v>19</v>
       </c>
       <c r="E80">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.4972451580988469</v>
       </c>
       <c r="F80">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.59669418971861632</v>
       </c>
       <c r="G80">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.62984386692520611</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I80">
+        <f t="shared" si="13"/>
+        <v>0.28846153846153844</v>
+      </c>
+      <c r="J80">
+        <f t="shared" si="14"/>
+        <v>0.34615384615384615</v>
+      </c>
+      <c r="K80">
+        <f t="shared" si="15"/>
+        <v>0.36538461538461536</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>17</v>
       </c>
@@ -2767,19 +3764,31 @@
         <v>20</v>
       </c>
       <c r="E81">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.51515151515151514</v>
       </c>
       <c r="F81">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.60606060606060608</v>
       </c>
       <c r="G81">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.60606060606060608</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I81">
+        <f t="shared" si="13"/>
+        <v>0.2982456140350877</v>
+      </c>
+      <c r="J81">
+        <f t="shared" si="14"/>
+        <v>0.35087719298245612</v>
+      </c>
+      <c r="K81">
+        <f t="shared" si="15"/>
+        <v>0.35087719298245612</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>15</v>
       </c>
@@ -2790,19 +3799,31 @@
         <v>18</v>
       </c>
       <c r="E82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.5181664018901001</v>
       </c>
       <c r="F82">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.58725525547544677</v>
       </c>
       <c r="G82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.6217996822681201</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I82">
+        <f t="shared" si="13"/>
+        <v>0.3</v>
+      </c>
+      <c r="J82">
+        <f t="shared" si="14"/>
+        <v>0.34</v>
+      </c>
+      <c r="K82">
+        <f t="shared" si="15"/>
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>15</v>
       </c>
@@ -2813,19 +3834,31 @@
         <v>19</v>
       </c>
       <c r="E83">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.4972451580988469</v>
       </c>
       <c r="F83">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.59669418971861632</v>
       </c>
       <c r="G83">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.62984386692520611</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I83">
+        <f t="shared" si="13"/>
+        <v>0.28846153846153844</v>
+      </c>
+      <c r="J83">
+        <f t="shared" si="14"/>
+        <v>0.34615384615384615</v>
+      </c>
+      <c r="K83">
+        <f t="shared" si="15"/>
+        <v>0.36538461538461536</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>17</v>
       </c>
@@ -2836,19 +3869,31 @@
         <v>18</v>
       </c>
       <c r="E84">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.55536579232708105</v>
       </c>
       <c r="F84">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.58803436834632106</v>
       </c>
       <c r="G84">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.58803436834632106</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I84">
+        <f t="shared" si="13"/>
+        <v>0.32075471698113206</v>
+      </c>
+      <c r="J84">
+        <f t="shared" si="14"/>
+        <v>0.33962264150943394</v>
+      </c>
+      <c r="K84">
+        <f t="shared" si="15"/>
+        <v>0.33962264150943394</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>16</v>
       </c>
@@ -2859,19 +3904,31 @@
         <v>20</v>
       </c>
       <c r="E85">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.50171779647125181</v>
       </c>
       <c r="F85">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.59578988330961158</v>
       </c>
       <c r="G85">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.62714724558906487</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I85">
+        <f t="shared" si="13"/>
+        <v>0.29090909090909089</v>
+      </c>
+      <c r="J85">
+        <f t="shared" si="14"/>
+        <v>0.34545454545454546</v>
+      </c>
+      <c r="K85">
+        <f t="shared" si="15"/>
+        <v>0.36363636363636365</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>15</v>
       </c>
@@ -2882,19 +3939,31 @@
         <v>19</v>
       </c>
       <c r="E86">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.4972451580988469</v>
       </c>
       <c r="F86">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.59669418971861632</v>
       </c>
       <c r="G86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.62984386692520611</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I86">
+        <f t="shared" si="13"/>
+        <v>0.28846153846153844</v>
+      </c>
+      <c r="J86">
+        <f t="shared" si="14"/>
+        <v>0.34615384615384615</v>
+      </c>
+      <c r="K86">
+        <f t="shared" si="15"/>
+        <v>0.36538461538461536</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>16</v>
       </c>
@@ -2905,19 +3974,31 @@
         <v>19</v>
       </c>
       <c r="E87">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.52158509331104674</v>
       </c>
       <c r="F87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.5867832299749276</v>
       </c>
       <c r="G87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.61938229830686797</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I87">
+        <f t="shared" si="13"/>
+        <v>0.30188679245283018</v>
+      </c>
+      <c r="J87">
+        <f t="shared" si="14"/>
+        <v>0.33962264150943394</v>
+      </c>
+      <c r="K87">
+        <f t="shared" si="15"/>
+        <v>0.35849056603773582</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>16</v>
       </c>
@@ -2928,19 +4009,31 @@
         <v>19</v>
       </c>
       <c r="E88">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.53156439534807631</v>
       </c>
       <c r="F88">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.56478717005733114</v>
       </c>
       <c r="G88">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.6312327194758407</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I88">
+        <f t="shared" si="13"/>
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="J88">
+        <f t="shared" si="14"/>
+        <v>0.32692307692307693</v>
+      </c>
+      <c r="K88">
+        <f t="shared" si="15"/>
+        <v>0.36538461538461536</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>15</v>
       </c>
@@ -2951,19 +4044,31 @@
         <v>19</v>
       </c>
       <c r="E89">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.50709255283710997</v>
       </c>
       <c r="F89">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.57470489321539131</v>
       </c>
       <c r="G89">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.64231723359367265</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I89">
+        <f t="shared" si="13"/>
+        <v>0.29411764705882354</v>
+      </c>
+      <c r="J89">
+        <f t="shared" si="14"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K89">
+        <f t="shared" si="15"/>
+        <v>0.37254901960784315</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>16</v>
       </c>
@@ -2974,16 +4079,28 @@
         <v>17</v>
       </c>
       <c r="E90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.56533220267005868</v>
       </c>
       <c r="F90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.56533220267005868</v>
       </c>
       <c r="G90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.60066546533693732</v>
+      </c>
+      <c r="I90">
+        <f t="shared" si="13"/>
+        <v>0.32653061224489793</v>
+      </c>
+      <c r="J90">
+        <f t="shared" si="14"/>
+        <v>0.32653061224489793</v>
+      </c>
+      <c r="K90">
+        <f t="shared" si="15"/>
+        <v>0.34693877551020408</v>
       </c>
     </row>
   </sheetData>
